--- a/MainTop/30.099.2026 Таня ВБ/print_print_sorted.xlsx
+++ b/MainTop/30.099.2026 Таня ВБ/print_print_sorted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\30.099.2026 Таня ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B360CB8F-D162-455B-B7D3-E504D718FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABF2787-D2CD-4ADD-9FDA-3C7CD6434E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -527,7 +527,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -536,25 +536,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99CCFF"/>
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF99CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFFFCCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFA07A"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
@@ -586,13 +598,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1224,1864 +1238,1864 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="2">
-        <v>4</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="B24" s="3">
+        <v>4</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="2">
-        <v>4</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="2">
-        <v>4</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="2">
-        <v>4</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="B27" s="3">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="2">
-        <v>4</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B28" s="3">
+        <v>4</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="2">
-        <v>4</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="B29" s="3">
+        <v>4</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="2">
-        <v>4</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30" s="3">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="2">
-        <v>4</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="B31" s="3">
+        <v>4</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="2">
-        <v>4</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="B32" s="3">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="2">
-        <v>4</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="2" t="s">
+      <c r="B33" s="3">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="2">
-        <v>4</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="B34" s="3">
+        <v>4</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="2">
-        <v>4</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="B35" s="3">
+        <v>4</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="2">
-        <v>4</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B36" s="3">
+        <v>4</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="2">
-        <v>4</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="B37" s="3">
+        <v>4</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="2">
-        <v>4</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="B38" s="3">
+        <v>4</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="2">
-        <v>4</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="B39" s="3">
+        <v>4</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="2">
-        <v>4</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="B40" s="3">
+        <v>4</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="2">
-        <v>4</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="B41" s="3">
+        <v>4</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="2">
-        <v>4</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="B42" s="3">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B43" s="2">
-        <v>4</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="B43" s="3">
+        <v>4</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="2">
-        <v>4</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="B44" s="3">
+        <v>4</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B45" s="2">
-        <v>4</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="B45" s="3">
+        <v>4</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="2">
-        <v>4</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="3">
+        <v>4</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="3">
-        <v>4</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="3" t="s">
+      <c r="B47" s="4">
+        <v>4</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="3">
-        <v>4</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D48" s="3" t="s">
+      <c r="B48" s="4">
+        <v>4</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B49" s="3">
-        <v>4</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D49" s="3" t="s">
+      <c r="B49" s="4">
+        <v>4</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="3">
-        <v>4</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="B50" s="4">
+        <v>4</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B51" s="3">
-        <v>4</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="B51" s="4">
+        <v>4</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="3">
-        <v>4</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="B52" s="4">
+        <v>4</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B53" s="3">
-        <v>4</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="3" t="s">
+      <c r="B53" s="4">
+        <v>4</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="3">
-        <v>4</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D54" s="3" t="s">
+      <c r="B54" s="4">
+        <v>4</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B55" s="3">
-        <v>4</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="3" t="s">
+      <c r="B55" s="4">
+        <v>4</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="3">
-        <v>4</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="3" t="s">
+      <c r="B56" s="4">
+        <v>4</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B57" s="3">
-        <v>4</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="3" t="s">
+      <c r="B57" s="4">
+        <v>4</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="3">
-        <v>4</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="3" t="s">
+      <c r="B58" s="4">
+        <v>4</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B59" s="3">
-        <v>4</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="3" t="s">
+      <c r="B59" s="4">
+        <v>4</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="3">
-        <v>4</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D60" s="3" t="s">
+      <c r="B60" s="4">
+        <v>4</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B61" s="3">
-        <v>4</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="3" t="s">
+      <c r="B61" s="4">
+        <v>4</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="3">
-        <v>4</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D62" s="3" t="s">
+      <c r="B62" s="4">
+        <v>4</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B63" s="3">
-        <v>4</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D63" s="3" t="s">
+      <c r="B63" s="4">
+        <v>4</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="3">
-        <v>4</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D64" s="3" t="s">
+      <c r="B64" s="4">
+        <v>4</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B65" s="3">
-        <v>4</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="B65" s="4">
+        <v>4</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="3">
-        <v>4</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="B66" s="4">
+        <v>4</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B67" s="3">
-        <v>4</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67" s="3" t="s">
+      <c r="B67" s="4">
+        <v>4</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B68" s="3">
-        <v>4</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="B68" s="4">
+        <v>4</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="3">
-        <v>4</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="B69" s="4">
+        <v>4</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="3">
-        <v>4</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="B70" s="4">
+        <v>4</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B71" s="3">
-        <v>4</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="B71" s="4">
+        <v>4</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B72" s="3">
-        <v>4</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D72" s="3" t="s">
+      <c r="B72" s="4">
+        <v>4</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B73" s="3">
-        <v>4</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D73" s="3" t="s">
+      <c r="B73" s="4">
+        <v>4</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="3">
-        <v>4</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D74" s="3" t="s">
+      <c r="B74" s="4">
+        <v>4</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B75" s="3">
-        <v>4</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="B75" s="4">
+        <v>4</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="3">
-        <v>4</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="3" t="s">
+      <c r="B76" s="4">
+        <v>4</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B77" s="3">
-        <v>4</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D77" s="3" t="s">
+      <c r="B77" s="4">
+        <v>4</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="3">
-        <v>4</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D78" s="3" t="s">
+      <c r="B78" s="4">
+        <v>4</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="3">
-        <v>4</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="3" t="s">
+      <c r="B79" s="4">
+        <v>4</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="3">
-        <v>4</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D80" s="3" t="s">
+      <c r="B80" s="4">
+        <v>4</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="3">
-        <v>4</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D81" s="3" t="s">
+      <c r="B81" s="4">
+        <v>4</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B82" s="3">
-        <v>4</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D82" s="3" t="s">
+      <c r="B82" s="4">
+        <v>4</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B83" s="3">
-        <v>4</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="3" t="s">
+      <c r="B83" s="4">
+        <v>4</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B84" s="3">
-        <v>4</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" s="3" t="s">
+      <c r="B84" s="4">
+        <v>4</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B85" s="3">
-        <v>4</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="3" t="s">
+      <c r="B85" s="4">
+        <v>4</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="3">
-        <v>4</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="3" t="s">
+      <c r="B86" s="4">
+        <v>4</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B87" s="3">
-        <v>4</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D87" s="3" t="s">
+      <c r="B87" s="4">
+        <v>4</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B88" s="3">
-        <v>4</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D88" s="3" t="s">
+      <c r="B88" s="4">
+        <v>4</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B89" s="3">
-        <v>4</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D89" s="3" t="s">
+      <c r="B89" s="4">
+        <v>4</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B90" s="3">
-        <v>4</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D90" s="3" t="s">
+      <c r="B90" s="4">
+        <v>4</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B91" s="3">
-        <v>4</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D91" s="3" t="s">
+      <c r="B91" s="5">
+        <v>4</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="3">
-        <v>4</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D92" s="3" t="s">
+      <c r="B92" s="5">
+        <v>4</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B93" s="3">
-        <v>4</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="3" t="s">
+      <c r="B93" s="5">
+        <v>4</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="3">
-        <v>4</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="3" t="s">
+      <c r="B94" s="5">
+        <v>4</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B95" s="3">
-        <v>4</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D95" s="3" t="s">
+      <c r="B95" s="5">
+        <v>4</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B96" s="3">
-        <v>4</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D96" s="3" t="s">
+      <c r="B96" s="5">
+        <v>4</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B97" s="3">
-        <v>4</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D97" s="3" t="s">
+      <c r="B97" s="5">
+        <v>4</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="3">
-        <v>4</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D98" s="3" t="s">
+      <c r="B98" s="5">
+        <v>4</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B99" s="3">
-        <v>4</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D99" s="3" t="s">
+      <c r="B99" s="5">
+        <v>4</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B100" s="3">
+      <c r="B100" s="5">
         <v>2</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D100" s="3" t="s">
+      <c r="C100" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B101" s="3">
+      <c r="B101" s="5">
         <v>16</v>
       </c>
-      <c r="C101" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D101" s="3" t="s">
+      <c r="C101" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B102" s="3">
+      <c r="B102" s="5">
         <v>8</v>
       </c>
-      <c r="C102" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D102" s="3" t="s">
+      <c r="C102" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D102" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="3">
-        <v>4</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D103" s="3" t="s">
+      <c r="B103" s="5">
+        <v>4</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D103" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B104" s="3">
-        <v>4</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D104" s="3" t="s">
+      <c r="B104" s="5">
+        <v>4</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D104" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B105" s="3">
-        <v>4</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D105" s="3" t="s">
+      <c r="B105" s="5">
+        <v>4</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D105" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B106" s="3">
-        <v>4</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D106" s="3" t="s">
+      <c r="B106" s="5">
+        <v>4</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D106" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B107" s="3">
-        <v>4</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D107" s="3" t="s">
+      <c r="B107" s="5">
+        <v>4</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D107" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B108" s="3">
-        <v>4</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D108" s="3" t="s">
+      <c r="B108" s="5">
+        <v>4</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B109" s="3">
-        <v>4</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D109" s="3" t="s">
+      <c r="B109" s="5">
+        <v>4</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D109" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B110" s="3">
-        <v>4</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D110" s="3" t="s">
+      <c r="B110" s="5">
+        <v>4</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B111" s="3">
-        <v>4</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D111" s="3" t="s">
+      <c r="B111" s="5">
+        <v>4</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D111" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B112" s="3">
-        <v>4</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D112" s="3" t="s">
+      <c r="B112" s="5">
+        <v>4</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D112" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B113" s="3">
-        <v>4</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D113" s="3" t="s">
+      <c r="B113" s="5">
+        <v>4</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D113" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B114" s="3">
-        <v>4</v>
-      </c>
-      <c r="C114" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D114" s="3" t="s">
+      <c r="B114" s="5">
+        <v>4</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D114" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B115" s="3">
-        <v>4</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D115" s="3" t="s">
+      <c r="B115" s="5">
+        <v>4</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D115" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B116" s="3">
-        <v>4</v>
-      </c>
-      <c r="C116" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D116" s="3" t="s">
+      <c r="B116" s="5">
+        <v>4</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D116" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+      <c r="A117" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B117" s="3">
-        <v>4</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D117" s="3" t="s">
+      <c r="B117" s="5">
+        <v>4</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D117" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B118" s="3">
-        <v>4</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D118" s="3" t="s">
+      <c r="B118" s="5">
+        <v>4</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D118" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+      <c r="A119" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B119" s="3">
-        <v>4</v>
-      </c>
-      <c r="C119" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D119" s="3" t="s">
+      <c r="B119" s="5">
+        <v>4</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D119" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B120" s="3">
-        <v>4</v>
-      </c>
-      <c r="C120" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D120" s="3" t="s">
+      <c r="B120" s="5">
+        <v>4</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D120" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B121" s="3">
-        <v>4</v>
-      </c>
-      <c r="C121" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D121" s="3" t="s">
+      <c r="B121" s="5">
+        <v>4</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D121" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B122" s="3">
-        <v>4</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D122" s="3" t="s">
+      <c r="B122" s="5">
+        <v>4</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D122" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B123" s="3">
-        <v>4</v>
-      </c>
-      <c r="C123" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D123" s="3" t="s">
+      <c r="B123" s="5">
+        <v>4</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D123" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B124" s="3">
-        <v>4</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D124" s="3" t="s">
+      <c r="B124" s="5">
+        <v>4</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D124" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B125" s="3">
-        <v>4</v>
-      </c>
-      <c r="C125" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D125" s="3" t="s">
+      <c r="B125" s="5">
+        <v>4</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D125" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B126" s="3">
-        <v>4</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D126" s="3" t="s">
+      <c r="B126" s="5">
+        <v>4</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D126" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B127" s="3">
-        <v>4</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D127" s="3" t="s">
+      <c r="B127" s="5">
+        <v>4</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D127" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B128" s="3">
-        <v>4</v>
-      </c>
-      <c r="C128" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D128" s="3" t="s">
+      <c r="B128" s="5">
+        <v>4</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B129" s="3">
-        <v>4</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D129" s="3" t="s">
+      <c r="B129" s="5">
+        <v>4</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B130" s="3">
-        <v>4</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D130" s="3" t="s">
+      <c r="B130" s="5">
+        <v>4</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B131" s="4">
-        <v>4</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D131" s="4" t="s">
+      <c r="B131" s="6">
+        <v>4</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B132" s="4">
-        <v>4</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D132" s="4" t="s">
+      <c r="B132" s="6">
+        <v>4</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B133" s="4">
-        <v>4</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D133" s="4" t="s">
+      <c r="B133" s="6">
+        <v>4</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B134" s="4">
-        <v>4</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D134" s="4" t="s">
+      <c r="B134" s="6">
+        <v>4</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B135" s="4">
-        <v>4</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D135" s="4" t="s">
+      <c r="B135" s="6">
+        <v>4</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B136" s="4">
-        <v>4</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D136" s="4" t="s">
+      <c r="B136" s="6">
+        <v>4</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D136" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B137" s="4">
-        <v>4</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D137" s="4" t="s">
+      <c r="B137" s="6">
+        <v>4</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B138" s="4">
-        <v>4</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D138" s="4" t="s">
+      <c r="B138" s="6">
+        <v>4</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D138" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B139" s="4">
-        <v>4</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D139" s="4" t="s">
+      <c r="B139" s="6">
+        <v>4</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D139" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="B140" s="4">
-        <v>4</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D140" s="4" t="s">
+      <c r="B140" s="6">
+        <v>4</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D140" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B141" s="4">
-        <v>4</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D141" s="4" t="s">
+      <c r="B141" s="6">
+        <v>4</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D141" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B142" s="4">
-        <v>4</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D142" s="4" t="s">
+      <c r="B142" s="6">
+        <v>4</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D142" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B143" s="4">
-        <v>4</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D143" s="4" t="s">
+      <c r="B143" s="6">
+        <v>4</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D143" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B144" s="4">
-        <v>4</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D144" s="4" t="s">
+      <c r="B144" s="6">
+        <v>4</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D144" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B145" s="4">
-        <v>4</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D145" s="4" t="s">
+      <c r="B145" s="6">
+        <v>4</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D145" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B146" s="4">
-        <v>4</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D146" s="4" t="s">
+      <c r="B146" s="6">
+        <v>4</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D146" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B147" s="4">
-        <v>4</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D147" s="4" t="s">
+      <c r="B147" s="6">
+        <v>4</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D147" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B148" s="4">
-        <v>4</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D148" s="4" t="s">
+      <c r="B148" s="6">
+        <v>4</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D148" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B149" s="4">
-        <v>4</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D149" s="4" t="s">
+      <c r="B149" s="6">
+        <v>4</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D149" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B150" s="5">
-        <v>4</v>
-      </c>
-      <c r="C150" s="5" t="s">
+      <c r="B150" s="7">
+        <v>4</v>
+      </c>
+      <c r="C150" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D150" s="5" t="s">
+      <c r="D150" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
+      <c r="A151" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="B151" s="5">
-        <v>4</v>
-      </c>
-      <c r="C151" s="5" t="s">
+      <c r="B151" s="7">
+        <v>4</v>
+      </c>
+      <c r="C151" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D151" s="5" t="s">
+      <c r="D151" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B152" s="5">
-        <v>4</v>
-      </c>
-      <c r="C152" s="5" t="s">
+      <c r="B152" s="7">
+        <v>4</v>
+      </c>
+      <c r="C152" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D152" s="5" t="s">
+      <c r="D152" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
+      <c r="A153" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B153" s="5">
-        <v>4</v>
-      </c>
-      <c r="C153" s="5" t="s">
+      <c r="B153" s="7">
+        <v>4</v>
+      </c>
+      <c r="C153" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D153" s="5" t="s">
+      <c r="D153" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B154" s="5">
-        <v>4</v>
-      </c>
-      <c r="C154" s="5" t="s">
+      <c r="B154" s="7">
+        <v>4</v>
+      </c>
+      <c r="C154" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D154" s="5" t="s">
+      <c r="D154" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
+      <c r="A155" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B155" s="5">
-        <v>4</v>
-      </c>
-      <c r="C155" s="5" t="s">
+      <c r="B155" s="7">
+        <v>4</v>
+      </c>
+      <c r="C155" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D155" s="5" t="s">
+      <c r="D155" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B156" s="5">
-        <v>4</v>
-      </c>
-      <c r="C156" s="5" t="s">
+      <c r="B156" s="7">
+        <v>4</v>
+      </c>
+      <c r="C156" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="D156" s="5" t="s">
+      <c r="D156" s="7" t="s">
         <v>6</v>
       </c>
     </row>
